--- a/data/dataset_komoditas.xlsx
+++ b/data/dataset_komoditas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Haykal Pasha Siregar\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\visdat\protein_maxxing\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B30CFC30-47B6-42D9-B28A-EF99441C1F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D9F9E1-2013-4044-A33C-8AF6A8422FAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{B07450B5-6875-445C-9D9C-4D27C15B6813}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B07450B5-6875-445C-9D9C-4D27C15B6813}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -218,7 +218,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -515,16 +515,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74D4BE92-6D60-4A63-A361-223008889C7B}">
   <dimension ref="A1:E954"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +541,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45292</v>
       </c>
@@ -558,7 +558,7 @@
         <v>145850</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45323</v>
       </c>
@@ -575,7 +575,7 @@
         <v>145850</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45352</v>
       </c>
@@ -592,7 +592,7 @@
         <v>145850</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45383</v>
       </c>
@@ -609,7 +609,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45413</v>
       </c>
@@ -626,7 +626,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>45444</v>
       </c>
@@ -643,7 +643,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>45474</v>
       </c>
@@ -660,7 +660,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>45505</v>
       </c>
@@ -677,7 +677,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>45536</v>
       </c>
@@ -694,7 +694,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>45566</v>
       </c>
@@ -711,7 +711,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>45597</v>
       </c>
@@ -728,7 +728,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>45627</v>
       </c>
@@ -745,7 +745,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>45658</v>
       </c>
@@ -762,7 +762,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>45689</v>
       </c>
@@ -779,7 +779,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>45717</v>
       </c>
@@ -796,7 +796,7 @@
         <v>171650</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>45748</v>
       </c>
@@ -813,7 +813,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>45778</v>
       </c>
@@ -830,7 +830,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>45809</v>
       </c>
@@ -847,7 +847,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>45839</v>
       </c>
@@ -864,7 +864,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>45870</v>
       </c>
@@ -881,7 +881,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>45901</v>
       </c>
@@ -898,7 +898,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>45931</v>
       </c>
@@ -915,7 +915,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>45962</v>
       </c>
@@ -932,7 +932,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>45992</v>
       </c>
@@ -949,7 +949,7 @@
         <v>146900</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>46023</v>
       </c>
@@ -966,7 +966,7 @@
         <v>146650</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>46054</v>
       </c>
@@ -983,7 +983,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>46082</v>
       </c>
@@ -1000,7 +1000,7 @@
         <v>148150</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>46113</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>152900</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>45292</v>
       </c>
@@ -1034,7 +1034,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>45323</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>45352</v>
       </c>
@@ -1068,7 +1068,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>45383</v>
       </c>
@@ -1085,7 +1085,7 @@
         <v>135250</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>45413</v>
       </c>
@@ -1102,7 +1102,7 @@
         <v>140650</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>45444</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>134900</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>45474</v>
       </c>
@@ -1136,7 +1136,7 @@
         <v>134900</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>45505</v>
       </c>
@@ -1153,7 +1153,7 @@
         <v>134900</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>45536</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>134900</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>45566</v>
       </c>
@@ -1187,7 +1187,7 @@
         <v>134900</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>45597</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>135500</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>45627</v>
       </c>
@@ -1221,7 +1221,7 @@
         <v>135500</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>45658</v>
       </c>
@@ -1238,7 +1238,7 @@
         <v>138250</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>45689</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>137950</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>45717</v>
       </c>
@@ -1272,7 +1272,7 @@
         <v>134400</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>45748</v>
       </c>
@@ -1289,7 +1289,7 @@
         <v>140400</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45778</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>134050</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45809</v>
       </c>
@@ -1323,7 +1323,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>45839</v>
       </c>
@@ -1340,7 +1340,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>45870</v>
       </c>
@@ -1357,7 +1357,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>45901</v>
       </c>
@@ -1374,7 +1374,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>45931</v>
       </c>
@@ -1391,7 +1391,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>45962</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>45992</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>133950</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>46023</v>
       </c>
@@ -1442,7 +1442,7 @@
         <v>134550</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>46054</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>136750</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>46082</v>
       </c>
@@ -1476,7 +1476,7 @@
         <v>137300</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>46113</v>
       </c>
@@ -1493,7 +1493,7 @@
         <v>137650</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>45292</v>
       </c>
@@ -1510,7 +1510,7 @@
         <v>148750</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>45323</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>148750</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>45352</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>149400</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>45383</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>45413</v>
       </c>
@@ -1578,7 +1578,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>45444</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>45474</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>45505</v>
       </c>
@@ -1629,7 +1629,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>45536</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>28075</v>
       </c>
       <c r="D66" s="2">
-        <f t="shared" ref="D66:E66" si="0">AVERAGE(D65,D67)</f>
+        <f t="shared" ref="D66" si="0">AVERAGE(D65,D67)</f>
         <v>42400</v>
       </c>
       <c r="E66" s="2">
@@ -1649,7 +1649,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>45566</v>
       </c>
@@ -1666,7 +1666,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>45597</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>45627</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>45658</v>
       </c>
@@ -1720,7 +1720,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>45689</v>
       </c>
@@ -1737,7 +1737,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>45717</v>
       </c>
@@ -1754,7 +1754,7 @@
         <v>148750</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>45748</v>
       </c>
@@ -1771,7 +1771,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>45778</v>
       </c>
@@ -1788,7 +1788,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>45809</v>
       </c>
@@ -1805,7 +1805,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>45839</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>45870</v>
       </c>
@@ -1839,7 +1839,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>45901</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>45931</v>
       </c>
@@ -1873,7 +1873,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>45962</v>
       </c>
@@ -1890,7 +1890,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>45992</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>46023</v>
       </c>
@@ -1924,7 +1924,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>46054</v>
       </c>
@@ -1941,7 +1941,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>46082</v>
       </c>
@@ -1958,7 +1958,7 @@
         <v>148150</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>46113</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>45292</v>
       </c>
@@ -1995,7 +1995,7 @@
         <v>138025</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>45323</v>
       </c>
@@ -2012,7 +2012,7 @@
         <v>126050</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>45352</v>
       </c>
@@ -2029,7 +2029,7 @@
         <v>126050</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>45383</v>
       </c>
@@ -2046,7 +2046,7 @@
         <v>128550</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>45413</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>45444</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>128150</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>45474</v>
       </c>
@@ -2097,7 +2097,7 @@
         <v>127900</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>45505</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>128150</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>45536</v>
       </c>
@@ -2131,7 +2131,7 @@
         <v>128150</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>45566</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>126450</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>45597</v>
       </c>
@@ -2165,7 +2165,7 @@
         <v>126450</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>45627</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>126350</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>45658</v>
       </c>
@@ -2202,7 +2202,7 @@
         <v>125425</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>45689</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>124500</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>45717</v>
       </c>
@@ -2236,7 +2236,7 @@
         <v>124800</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>45748</v>
       </c>
@@ -2253,7 +2253,7 @@
         <v>127100</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>45778</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>124500</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>45809</v>
       </c>
@@ -2287,7 +2287,7 @@
         <v>124500</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>45839</v>
       </c>
@@ -2304,7 +2304,7 @@
         <v>124400</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>45870</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>125200</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>45901</v>
       </c>
@@ -2338,7 +2338,7 @@
         <v>125200</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>45931</v>
       </c>
@@ -2355,7 +2355,7 @@
         <v>125200</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>45962</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>125200</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>45992</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>125200</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>46023</v>
       </c>
@@ -2406,7 +2406,7 @@
         <v>126650</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>46054</v>
       </c>
@@ -2423,7 +2423,7 @@
         <v>128000</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>46082</v>
       </c>
@@ -2440,7 +2440,7 @@
         <v>129250</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>46113</v>
       </c>
@@ -2457,7 +2457,7 @@
         <v>131150</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>45292</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>99250</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>45323</v>
       </c>
@@ -2491,7 +2491,7 @@
         <v>99250</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>45352</v>
       </c>
@@ -2508,7 +2508,7 @@
         <v>99250</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>45383</v>
       </c>
@@ -2525,7 +2525,7 @@
         <v>100750</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>45413</v>
       </c>
@@ -2542,7 +2542,7 @@
         <v>99500</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>45444</v>
       </c>
@@ -2559,7 +2559,7 @@
         <v>99500</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>45474</v>
       </c>
@@ -2576,7 +2576,7 @@
         <v>99500</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>45505</v>
       </c>
@@ -2593,7 +2593,7 @@
         <v>99200</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>45536</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>99200</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>45566</v>
       </c>
@@ -2627,7 +2627,7 @@
         <v>99200</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>45597</v>
       </c>
@@ -2644,7 +2644,7 @@
         <v>99200</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>45627</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>99200</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>45658</v>
       </c>
@@ -2678,7 +2678,7 @@
         <v>99200</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>45689</v>
       </c>
@@ -2695,7 +2695,7 @@
         <v>99200</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>45717</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>100250</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>45748</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>100700</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>45778</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>95700</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>45809</v>
       </c>
@@ -2763,7 +2763,7 @@
         <v>100250</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>45839</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>100450</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>45870</v>
       </c>
@@ -2797,7 +2797,7 @@
         <v>115850</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>45901</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>115850</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>45931</v>
       </c>
@@ -2831,7 +2831,7 @@
         <v>115850</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>45962</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>45992</v>
       </c>
@@ -2865,7 +2865,7 @@
         <v>115450</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>46023</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>123350</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>46054</v>
       </c>
@@ -2899,7 +2899,7 @@
         <v>122950</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>46082</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>125850</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>46113</v>
       </c>
@@ -2933,7 +2933,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>45292</v>
       </c>
@@ -2950,7 +2950,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>45323</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>45352</v>
       </c>
@@ -2984,7 +2984,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>45383</v>
       </c>
@@ -3001,7 +3001,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>45413</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>45444</v>
       </c>
@@ -3035,7 +3035,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>45474</v>
       </c>
@@ -3052,7 +3052,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>45505</v>
       </c>
@@ -3069,7 +3069,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>45536</v>
       </c>
@@ -3086,7 +3086,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>45566</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>45597</v>
       </c>
@@ -3120,7 +3120,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>45627</v>
       </c>
@@ -3137,7 +3137,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>45658</v>
       </c>
@@ -3154,7 +3154,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>45689</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>45717</v>
       </c>
@@ -3188,7 +3188,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>45748</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>45778</v>
       </c>
@@ -3222,7 +3222,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>45809</v>
       </c>
@@ -3239,7 +3239,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>45839</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>45870</v>
       </c>
@@ -3273,7 +3273,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>45901</v>
       </c>
@@ -3290,7 +3290,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>45931</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>45962</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>45992</v>
       </c>
@@ -3341,7 +3341,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>46023</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>142500</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>46054</v>
       </c>
@@ -3375,7 +3375,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>46082</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>46113</v>
       </c>
@@ -3409,7 +3409,7 @@
         <v>151250</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>45292</v>
       </c>
@@ -3429,7 +3429,7 @@
         <v>143450</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>45323</v>
       </c>
@@ -3446,7 +3446,7 @@
         <v>135650</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>45352</v>
       </c>
@@ -3463,7 +3463,7 @@
         <v>135650</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>45383</v>
       </c>
@@ -3480,7 +3480,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>45413</v>
       </c>
@@ -3497,7 +3497,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>45444</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>45474</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>45505</v>
       </c>
@@ -3548,7 +3548,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>45536</v>
       </c>
@@ -3565,7 +3565,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>45566</v>
       </c>
@@ -3582,7 +3582,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>45597</v>
       </c>
@@ -3599,7 +3599,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>45627</v>
       </c>
@@ -3616,7 +3616,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>45658</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>45689</v>
       </c>
@@ -3650,7 +3650,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>45717</v>
       </c>
@@ -3667,7 +3667,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>45748</v>
       </c>
@@ -3684,7 +3684,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>45778</v>
       </c>
@@ -3701,7 +3701,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>45809</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>45839</v>
       </c>
@@ -3735,7 +3735,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>45870</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>45901</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>45931</v>
       </c>
@@ -3786,7 +3786,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>45962</v>
       </c>
@@ -3803,7 +3803,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>45992</v>
       </c>
@@ -3820,7 +3820,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>46023</v>
       </c>
@@ -3837,7 +3837,7 @@
         <v>135950</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>46054</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>135650</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>46082</v>
       </c>
@@ -3871,7 +3871,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>46113</v>
       </c>
@@ -3888,7 +3888,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>45292</v>
       </c>
@@ -3908,7 +3908,7 @@
         <v>143125</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>45323</v>
       </c>
@@ -3925,7 +3925,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>45352</v>
       </c>
@@ -3942,7 +3942,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>45383</v>
       </c>
@@ -3959,7 +3959,7 @@
         <v>139400</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>45413</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>45444</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>45474</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>45505</v>
       </c>
@@ -4027,7 +4027,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>45536</v>
       </c>
@@ -4044,7 +4044,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>45566</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>45597</v>
       </c>
@@ -4078,7 +4078,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>45627</v>
       </c>
@@ -4095,7 +4095,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>45658</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>45689</v>
       </c>
@@ -4129,7 +4129,7 @@
         <v>139100</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>45717</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>139100</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>45748</v>
       </c>
@@ -4163,7 +4163,7 @@
         <v>146600</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>45778</v>
       </c>
@@ -4180,7 +4180,7 @@
         <v>139100</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>45809</v>
       </c>
@@ -4197,7 +4197,7 @@
         <v>139100</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>45839</v>
       </c>
@@ -4214,7 +4214,7 @@
         <v>139100</v>
       </c>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>45870</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>139100</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>45901</v>
       </c>
@@ -4248,7 +4248,7 @@
         <v>139100</v>
       </c>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>45931</v>
       </c>
@@ -4265,7 +4265,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>45962</v>
       </c>
@@ -4282,7 +4282,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>45992</v>
       </c>
@@ -4299,7 +4299,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>46023</v>
       </c>
@@ -4316,7 +4316,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>46054</v>
       </c>
@@ -4333,7 +4333,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>46082</v>
       </c>
@@ -4350,7 +4350,7 @@
         <v>142500</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>46113</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>141900</v>
       </c>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>45292</v>
       </c>
@@ -4384,7 +4384,7 @@
         <v>139700</v>
       </c>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>45323</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>132850</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>45352</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>132850</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>45383</v>
       </c>
@@ -4435,7 +4435,7 @@
         <v>135650</v>
       </c>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>45413</v>
       </c>
@@ -4452,7 +4452,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>45444</v>
       </c>
@@ -4469,7 +4469,7 @@
         <v>135650</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>45474</v>
       </c>
@@ -4486,7 +4486,7 @@
         <v>135950</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>45505</v>
       </c>
@@ -4503,7 +4503,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>45536</v>
       </c>
@@ -4520,7 +4520,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>45566</v>
       </c>
@@ -4537,7 +4537,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>45597</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>45627</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>45658</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>134925</v>
       </c>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>45689</v>
       </c>
@@ -4608,7 +4608,7 @@
         <v>134850</v>
       </c>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>45717</v>
       </c>
@@ -4625,7 +4625,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>45748</v>
       </c>
@@ -4642,7 +4642,7 @@
         <v>142850</v>
       </c>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>45778</v>
       </c>
@@ -4659,7 +4659,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>45809</v>
       </c>
@@ -4676,7 +4676,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>45839</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>45870</v>
       </c>
@@ -4710,7 +4710,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>45901</v>
       </c>
@@ -4727,7 +4727,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>45931</v>
       </c>
@@ -4744,7 +4744,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>45962</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>45992</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>46023</v>
       </c>
@@ -4795,7 +4795,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>46054</v>
       </c>
@@ -4812,7 +4812,7 @@
         <v>135650</v>
       </c>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>46082</v>
       </c>
@@ -4829,7 +4829,7 @@
         <v>145950</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>46113</v>
       </c>
@@ -4846,7 +4846,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>45292</v>
       </c>
@@ -4866,7 +4866,7 @@
         <v>135325</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>45323</v>
       </c>
@@ -4883,7 +4883,7 @@
         <v>129400</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>45352</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>129400</v>
       </c>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>45383</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>45413</v>
       </c>
@@ -4934,7 +4934,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>45444</v>
       </c>
@@ -4951,7 +4951,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>45474</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>45505</v>
       </c>
@@ -4985,7 +4985,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>45536</v>
       </c>
@@ -5002,7 +5002,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>45566</v>
       </c>
@@ -5019,7 +5019,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>45597</v>
       </c>
@@ -5036,7 +5036,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>45627</v>
       </c>
@@ -5053,7 +5053,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>45658</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>45689</v>
       </c>
@@ -5087,7 +5087,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>45717</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>133150</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>45748</v>
       </c>
@@ -5121,7 +5121,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>45778</v>
       </c>
@@ -5138,7 +5138,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>45809</v>
       </c>
@@ -5155,7 +5155,7 @@
         <v>128750</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>45839</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>128750</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>45870</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>128750</v>
       </c>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>45901</v>
       </c>
@@ -5206,7 +5206,7 @@
         <v>128750</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>45931</v>
       </c>
@@ -5223,7 +5223,7 @@
         <v>128750</v>
       </c>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>45962</v>
       </c>
@@ -5240,7 +5240,7 @@
         <v>128750</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>45992</v>
       </c>
@@ -5257,7 +5257,7 @@
         <v>129400</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>46023</v>
       </c>
@@ -5274,7 +5274,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>46054</v>
       </c>
@@ -5291,7 +5291,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>46082</v>
       </c>
@@ -5308,7 +5308,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>46113</v>
       </c>
@@ -5325,7 +5325,7 @@
         <v>134100</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>45292</v>
       </c>
@@ -5342,7 +5342,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>45323</v>
       </c>
@@ -5359,7 +5359,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>45352</v>
       </c>
@@ -5376,7 +5376,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>45383</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>133350</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>45413</v>
       </c>
@@ -5410,7 +5410,7 @@
         <v>134150</v>
       </c>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>45444</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>45474</v>
       </c>
@@ -5444,7 +5444,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>45505</v>
       </c>
@@ -5461,7 +5461,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>45536</v>
       </c>
@@ -5478,7 +5478,7 @@
         <v>134150</v>
       </c>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>45566</v>
       </c>
@@ -5495,7 +5495,7 @@
         <v>134150</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>45597</v>
       </c>
@@ -5512,7 +5512,7 @@
         <v>134150</v>
       </c>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>45627</v>
       </c>
@@ -5529,7 +5529,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>45658</v>
       </c>
@@ -5546,7 +5546,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>45689</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>129150</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>45717</v>
       </c>
@@ -5580,7 +5580,7 @@
         <v>133350</v>
       </c>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>45748</v>
       </c>
@@ -5597,7 +5597,7 @@
         <v>144150</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A298" s="1">
         <v>45778</v>
       </c>
@@ -5614,7 +5614,7 @@
         <v>133350</v>
       </c>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A299" s="1">
         <v>45809</v>
       </c>
@@ -5631,7 +5631,7 @@
         <v>133350</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A300" s="1">
         <v>45839</v>
       </c>
@@ -5648,7 +5648,7 @@
         <v>133350</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A301" s="1">
         <v>45870</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>133350</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A302" s="1">
         <v>45901</v>
       </c>
@@ -5682,7 +5682,7 @@
         <v>132700</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A303" s="1">
         <v>45931</v>
       </c>
@@ -5699,7 +5699,7 @@
         <v>132700</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A304" s="1">
         <v>45962</v>
       </c>
@@ -5716,7 +5716,7 @@
         <v>132700</v>
       </c>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A305" s="1">
         <v>45992</v>
       </c>
@@ -5733,7 +5733,7 @@
         <v>132700</v>
       </c>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A306" s="1">
         <v>46023</v>
       </c>
@@ -5750,7 +5750,7 @@
         <v>137700</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A307" s="1">
         <v>46054</v>
       </c>
@@ -5767,7 +5767,7 @@
         <v>144600</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A308" s="1">
         <v>46082</v>
       </c>
@@ -5784,7 +5784,7 @@
         <v>147100</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A309" s="1">
         <v>46113</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A310" s="1">
         <v>45292</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>139600</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A311" s="1">
         <v>45323</v>
       </c>
@@ -5835,7 +5835,7 @@
         <v>139250</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A312" s="1">
         <v>45352</v>
       </c>
@@ -5852,7 +5852,7 @@
         <v>138950</v>
       </c>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A313" s="1">
         <v>45383</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>141050</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A314" s="1">
         <v>45413</v>
       </c>
@@ -5886,7 +5886,7 @@
         <v>141600</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A315" s="1">
         <v>45444</v>
       </c>
@@ -5903,7 +5903,7 @@
         <v>140850</v>
       </c>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A316" s="1">
         <v>45474</v>
       </c>
@@ -5920,7 +5920,7 @@
         <v>140900</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A317" s="1">
         <v>45505</v>
       </c>
@@ -5937,7 +5937,7 @@
         <v>140850</v>
       </c>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A318" s="1">
         <v>45536</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>140450</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A319" s="1">
         <v>45566</v>
       </c>
@@ -5971,7 +5971,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A320" s="1">
         <v>45597</v>
       </c>
@@ -5988,7 +5988,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A321" s="1">
         <v>45627</v>
       </c>
@@ -6005,7 +6005,7 @@
         <v>139950</v>
       </c>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A322" s="1">
         <v>45658</v>
       </c>
@@ -6022,7 +6022,7 @@
         <v>140900</v>
       </c>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A323" s="1">
         <v>45689</v>
       </c>
@@ -6039,7 +6039,7 @@
         <v>139050</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>45717</v>
       </c>
@@ -6056,7 +6056,7 @@
         <v>143800</v>
       </c>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>45748</v>
       </c>
@@ -6073,7 +6073,7 @@
         <v>150150</v>
       </c>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>45778</v>
       </c>
@@ -6090,7 +6090,7 @@
         <v>140050</v>
       </c>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>45809</v>
       </c>
@@ -6107,7 +6107,7 @@
         <v>139700</v>
       </c>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>45839</v>
       </c>
@@ -6124,7 +6124,7 @@
         <v>139050</v>
       </c>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>45870</v>
       </c>
@@ -6141,7 +6141,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>45901</v>
       </c>
@@ -6158,7 +6158,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>45931</v>
       </c>
@@ -6175,7 +6175,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>45962</v>
       </c>
@@ -6192,7 +6192,7 @@
         <v>138600</v>
       </c>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>45992</v>
       </c>
@@ -6209,7 +6209,7 @@
         <v>138900</v>
       </c>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>46023</v>
       </c>
@@ -6226,7 +6226,7 @@
         <v>139100</v>
       </c>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>46054</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>141200</v>
       </c>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>46082</v>
       </c>
@@ -6260,7 +6260,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>46113</v>
       </c>
@@ -6277,7 +6277,7 @@
         <v>152250</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A338" s="1">
         <v>45292</v>
       </c>
@@ -6297,7 +6297,7 @@
         <v>146950</v>
       </c>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A339" s="1">
         <v>45323</v>
       </c>
@@ -6314,7 +6314,7 @@
         <v>141650</v>
       </c>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A340" s="1">
         <v>45352</v>
       </c>
@@ -6331,7 +6331,7 @@
         <v>141650</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A341" s="1">
         <v>45383</v>
       </c>
@@ -6348,7 +6348,7 @@
         <v>144150</v>
       </c>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A342" s="1">
         <v>45413</v>
       </c>
@@ -6365,7 +6365,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A343" s="1">
         <v>45444</v>
       </c>
@@ -6382,7 +6382,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A344" s="1">
         <v>45474</v>
       </c>
@@ -6399,7 +6399,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A345" s="1">
         <v>45505</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A346" s="1">
         <v>45536</v>
       </c>
@@ -6433,7 +6433,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A347" s="1">
         <v>45566</v>
       </c>
@@ -6450,7 +6450,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A348" s="1">
         <v>45597</v>
       </c>
@@ -6467,7 +6467,7 @@
         <v>136650</v>
       </c>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A349" s="1">
         <v>45627</v>
       </c>
@@ -6484,7 +6484,7 @@
         <v>134600</v>
       </c>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A350" s="1">
         <v>45658</v>
       </c>
@@ -6504,7 +6504,7 @@
         <v>134600</v>
       </c>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A351" s="1">
         <v>45689</v>
       </c>
@@ -6521,7 +6521,7 @@
         <v>134600</v>
       </c>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A352" s="1">
         <v>45717</v>
       </c>
@@ -6538,7 +6538,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A353" s="1">
         <v>45748</v>
       </c>
@@ -6555,7 +6555,7 @@
         <v>140850</v>
       </c>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A354" s="1">
         <v>45778</v>
       </c>
@@ -6572,7 +6572,7 @@
         <v>137900</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A355" s="1">
         <v>45809</v>
       </c>
@@ -6589,7 +6589,7 @@
         <v>137900</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A356" s="1">
         <v>45839</v>
       </c>
@@ -6606,7 +6606,7 @@
         <v>137900</v>
       </c>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A357" s="1">
         <v>45870</v>
       </c>
@@ -6623,7 +6623,7 @@
         <v>135850</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A358" s="1">
         <v>45901</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>135850</v>
       </c>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A359" s="1">
         <v>45931</v>
       </c>
@@ -6657,7 +6657,7 @@
         <v>135400</v>
       </c>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A360" s="1">
         <v>45962</v>
       </c>
@@ -6674,7 +6674,7 @@
         <v>135400</v>
       </c>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A361" s="1">
         <v>45992</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>135400</v>
       </c>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A362" s="1">
         <v>46023</v>
       </c>
@@ -6708,7 +6708,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A363" s="1">
         <v>46054</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>144250</v>
       </c>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A364" s="1">
         <v>46082</v>
       </c>
@@ -6742,7 +6742,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A365" s="1">
         <v>46113</v>
       </c>
@@ -6759,7 +6759,7 @@
         <v>149700</v>
       </c>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A366" s="1">
         <v>45292</v>
       </c>
@@ -6776,7 +6776,7 @@
         <v>126750</v>
       </c>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A367" s="1">
         <v>45323</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>129000</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A368" s="1">
         <v>45352</v>
       </c>
@@ -6810,7 +6810,7 @@
         <v>128700</v>
       </c>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A369" s="1">
         <v>45383</v>
       </c>
@@ -6827,7 +6827,7 @@
         <v>128700</v>
       </c>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A370" s="1">
         <v>45413</v>
       </c>
@@ -6844,7 +6844,7 @@
         <v>126100</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A371" s="1">
         <v>45444</v>
       </c>
@@ -6861,7 +6861,7 @@
         <v>128250</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A372" s="1">
         <v>45474</v>
       </c>
@@ -6878,7 +6878,7 @@
         <v>128200</v>
       </c>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A373" s="1">
         <v>45505</v>
       </c>
@@ -6895,7 +6895,7 @@
         <v>128150</v>
       </c>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A374" s="1">
         <v>45536</v>
       </c>
@@ -6912,7 +6912,7 @@
         <v>127900</v>
       </c>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A375" s="1">
         <v>45566</v>
       </c>
@@ -6929,7 +6929,7 @@
         <v>128050</v>
       </c>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A376" s="1">
         <v>45597</v>
       </c>
@@ -6946,7 +6946,7 @@
         <v>128050</v>
       </c>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A377" s="1">
         <v>45627</v>
       </c>
@@ -6963,7 +6963,7 @@
         <v>128050</v>
       </c>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A378" s="1">
         <v>45658</v>
       </c>
@@ -6980,7 +6980,7 @@
         <v>127400</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A379" s="1">
         <v>45689</v>
       </c>
@@ -6997,7 +6997,7 @@
         <v>128250</v>
       </c>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A380" s="1">
         <v>45717</v>
       </c>
@@ -7014,7 +7014,7 @@
         <v>128750</v>
       </c>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A381" s="1">
         <v>45748</v>
       </c>
@@ -7031,7 +7031,7 @@
         <v>137450</v>
       </c>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A382" s="1">
         <v>45778</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>128200</v>
       </c>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A383" s="1">
         <v>45809</v>
       </c>
@@ -7065,7 +7065,7 @@
         <v>128100</v>
       </c>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A384" s="1">
         <v>45839</v>
       </c>
@@ -7082,7 +7082,7 @@
         <v>127900</v>
       </c>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A385" s="1">
         <v>45870</v>
       </c>
@@ -7099,7 +7099,7 @@
         <v>127900</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A386" s="1">
         <v>45901</v>
       </c>
@@ -7116,7 +7116,7 @@
         <v>127900</v>
       </c>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A387" s="1">
         <v>45931</v>
       </c>
@@ -7133,7 +7133,7 @@
         <v>127900</v>
       </c>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A388" s="1">
         <v>45962</v>
       </c>
@@ -7150,7 +7150,7 @@
         <v>127900</v>
       </c>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A389" s="1">
         <v>45992</v>
       </c>
@@ -7167,7 +7167,7 @@
         <v>127900</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A390" s="1">
         <v>46023</v>
       </c>
@@ -7184,7 +7184,7 @@
         <v>126950</v>
       </c>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A391" s="1">
         <v>46054</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>128300</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A392" s="1">
         <v>46082</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>130150</v>
       </c>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A393" s="1">
         <v>46113</v>
       </c>
@@ -7235,7 +7235,7 @@
         <v>139050</v>
       </c>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A394" s="1">
         <v>45292</v>
       </c>
@@ -7252,7 +7252,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A395" s="1">
         <v>45323</v>
       </c>
@@ -7269,7 +7269,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A396" s="1">
         <v>45352</v>
       </c>
@@ -7286,7 +7286,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A397" s="1">
         <v>45383</v>
       </c>
@@ -7303,7 +7303,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A398" s="1">
         <v>45413</v>
       </c>
@@ -7320,7 +7320,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A399" s="1">
         <v>45444</v>
       </c>
@@ -7337,7 +7337,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A400" s="1">
         <v>45474</v>
       </c>
@@ -7354,7 +7354,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A401" s="1">
         <v>45505</v>
       </c>
@@ -7371,7 +7371,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A402" s="1">
         <v>45536</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A403" s="1">
         <v>45566</v>
       </c>
@@ -7405,7 +7405,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A404" s="1">
         <v>45597</v>
       </c>
@@ -7422,7 +7422,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A405" s="1">
         <v>45627</v>
       </c>
@@ -7439,7 +7439,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A406" s="1">
         <v>45658</v>
       </c>
@@ -7456,7 +7456,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A407" s="1">
         <v>45689</v>
       </c>
@@ -7473,7 +7473,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A408" s="1">
         <v>45717</v>
       </c>
@@ -7490,7 +7490,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A409" s="1">
         <v>45748</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A410" s="1">
         <v>45778</v>
       </c>
@@ -7524,7 +7524,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A411" s="1">
         <v>45809</v>
       </c>
@@ -7541,7 +7541,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A412" s="1">
         <v>45839</v>
       </c>
@@ -7558,7 +7558,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A413" s="1">
         <v>45870</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A414" s="1">
         <v>45901</v>
       </c>
@@ -7592,7 +7592,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A415" s="1">
         <v>45931</v>
       </c>
@@ -7609,7 +7609,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A416" s="1">
         <v>45962</v>
       </c>
@@ -7626,7 +7626,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A417" s="1">
         <v>45992</v>
       </c>
@@ -7643,7 +7643,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A418" s="1">
         <v>46023</v>
       </c>
@@ -7660,7 +7660,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A419" s="1">
         <v>46054</v>
       </c>
@@ -7677,7 +7677,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A420" s="1">
         <v>46082</v>
       </c>
@@ -7694,7 +7694,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A421" s="1">
         <v>46113</v>
       </c>
@@ -7711,7 +7711,7 @@
         <v>150650</v>
       </c>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A422" s="1">
         <v>45292</v>
       </c>
@@ -7728,7 +7728,7 @@
         <v>118200</v>
       </c>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A423" s="1">
         <v>45323</v>
       </c>
@@ -7745,7 +7745,7 @@
         <v>117750</v>
       </c>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A424" s="1">
         <v>45352</v>
       </c>
@@ -7762,7 +7762,7 @@
         <v>117750</v>
       </c>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A425" s="1">
         <v>45383</v>
       </c>
@@ -7779,7 +7779,7 @@
         <v>119750</v>
       </c>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A426" s="1">
         <v>45413</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>121350</v>
       </c>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A427" s="1">
         <v>45444</v>
       </c>
@@ -7813,7 +7813,7 @@
         <v>120850</v>
       </c>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A428" s="1">
         <v>45474</v>
       </c>
@@ -7830,7 +7830,7 @@
         <v>120100</v>
       </c>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A429" s="1">
         <v>45505</v>
       </c>
@@ -7847,7 +7847,7 @@
         <v>120200</v>
       </c>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A430" s="1">
         <v>45536</v>
       </c>
@@ -7864,7 +7864,7 @@
         <v>120400</v>
       </c>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A431" s="1">
         <v>45566</v>
       </c>
@@ -7881,7 +7881,7 @@
         <v>120600</v>
       </c>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A432" s="1">
         <v>45597</v>
       </c>
@@ -7898,7 +7898,7 @@
         <v>121850</v>
       </c>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A433" s="1">
         <v>45627</v>
       </c>
@@ -7915,7 +7915,7 @@
         <v>121850</v>
       </c>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A434" s="1">
         <v>45658</v>
       </c>
@@ -7932,7 +7932,7 @@
         <v>121150</v>
       </c>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A435" s="1">
         <v>45689</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>120450</v>
       </c>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A436" s="1">
         <v>45717</v>
       </c>
@@ -7966,7 +7966,7 @@
         <v>121200</v>
       </c>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A437" s="1">
         <v>45748</v>
       </c>
@@ -7983,7 +7983,7 @@
         <v>125100</v>
       </c>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A438" s="1">
         <v>45778</v>
       </c>
@@ -8000,7 +8000,7 @@
         <v>121000</v>
       </c>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A439" s="1">
         <v>45809</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>121150</v>
       </c>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A440" s="1">
         <v>45839</v>
       </c>
@@ -8034,7 +8034,7 @@
         <v>120450</v>
       </c>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A441" s="1">
         <v>45870</v>
       </c>
@@ -8051,7 +8051,7 @@
         <v>120400</v>
       </c>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A442" s="1">
         <v>45901</v>
       </c>
@@ -8068,7 +8068,7 @@
         <v>120000</v>
       </c>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A443" s="1">
         <v>45931</v>
       </c>
@@ -8085,7 +8085,7 @@
         <v>121850</v>
       </c>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A444" s="1">
         <v>45962</v>
       </c>
@@ -8102,7 +8102,7 @@
         <v>122700</v>
       </c>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A445" s="1">
         <v>45992</v>
       </c>
@@ -8119,7 +8119,7 @@
         <v>123350</v>
       </c>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A446" s="1">
         <v>46023</v>
       </c>
@@ -8136,7 +8136,7 @@
         <v>123800</v>
       </c>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A447" s="1">
         <v>46054</v>
       </c>
@@ -8153,7 +8153,7 @@
         <v>124450</v>
       </c>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A448" s="1">
         <v>46082</v>
       </c>
@@ -8170,7 +8170,7 @@
         <v>124950</v>
       </c>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A449" s="1">
         <v>46113</v>
       </c>
@@ -8187,7 +8187,7 @@
         <v>129550</v>
       </c>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A450" s="1">
         <v>45292</v>
       </c>
@@ -8204,7 +8204,7 @@
         <v>120650</v>
       </c>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A451" s="1">
         <v>45323</v>
       </c>
@@ -8221,7 +8221,7 @@
         <v>126600</v>
       </c>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A452" s="1">
         <v>45352</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>126600</v>
       </c>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A453" s="1">
         <v>45383</v>
       </c>
@@ -8255,7 +8255,7 @@
         <v>119950</v>
       </c>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A454" s="1">
         <v>45413</v>
       </c>
@@ -8272,7 +8272,7 @@
         <v>126600</v>
       </c>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A455" s="1">
         <v>45444</v>
       </c>
@@ -8289,7 +8289,7 @@
         <v>126300</v>
       </c>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A456" s="1">
         <v>45474</v>
       </c>
@@ -8306,7 +8306,7 @@
         <v>126300</v>
       </c>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A457" s="1">
         <v>45505</v>
       </c>
@@ -8323,7 +8323,7 @@
         <v>126300</v>
       </c>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A458" s="1">
         <v>45536</v>
       </c>
@@ -8340,7 +8340,7 @@
         <v>125950</v>
       </c>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A459" s="1">
         <v>45566</v>
       </c>
@@ -8357,7 +8357,7 @@
         <v>127200</v>
       </c>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A460" s="1">
         <v>45597</v>
       </c>
@@ -8374,7 +8374,7 @@
         <v>127200</v>
       </c>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A461" s="1">
         <v>45627</v>
       </c>
@@ -8391,7 +8391,7 @@
         <v>132200</v>
       </c>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A462" s="1">
         <v>45658</v>
       </c>
@@ -8408,7 +8408,7 @@
         <v>132850</v>
       </c>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A463" s="1">
         <v>45689</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>132850</v>
       </c>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A464" s="1">
         <v>45717</v>
       </c>
@@ -8442,7 +8442,7 @@
         <v>132850</v>
       </c>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A465" s="1">
         <v>45748</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>132850</v>
       </c>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A466" s="1">
         <v>45778</v>
       </c>
@@ -8476,7 +8476,7 @@
         <v>132200</v>
       </c>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A467" s="1">
         <v>45809</v>
       </c>
@@ -8493,7 +8493,7 @@
         <v>132200</v>
       </c>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A468" s="1">
         <v>45839</v>
       </c>
@@ -8510,7 +8510,7 @@
         <v>132200</v>
       </c>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A469" s="1">
         <v>45870</v>
       </c>
@@ -8527,7 +8527,7 @@
         <v>132200</v>
       </c>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A470" s="1">
         <v>45901</v>
       </c>
@@ -8544,7 +8544,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A471" s="1">
         <v>45931</v>
       </c>
@@ -8561,7 +8561,7 @@
         <v>134100</v>
       </c>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A472" s="1">
         <v>45962</v>
       </c>
@@ -8578,7 +8578,7 @@
         <v>134850</v>
       </c>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A473" s="1">
         <v>45992</v>
       </c>
@@ -8595,7 +8595,7 @@
         <v>134850</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A474" s="1">
         <v>46023</v>
       </c>
@@ -8612,7 +8612,7 @@
         <v>134850</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A475" s="1">
         <v>46054</v>
       </c>
@@ -8629,7 +8629,7 @@
         <v>134850</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A476" s="1">
         <v>46082</v>
       </c>
@@ -8646,7 +8646,7 @@
         <v>134250</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A477" s="1">
         <v>46113</v>
       </c>
@@ -8663,7 +8663,7 @@
         <v>134250</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A478" s="1">
         <v>45292</v>
       </c>
@@ -8680,7 +8680,7 @@
         <v>117650</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A479" s="1">
         <v>45323</v>
       </c>
@@ -8697,7 +8697,7 @@
         <v>117650</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A480" s="1">
         <v>45352</v>
       </c>
@@ -8714,7 +8714,7 @@
         <v>117650</v>
       </c>
     </row>
-    <row r="481" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A481" s="1">
         <v>45383</v>
       </c>
@@ -8731,7 +8731,7 @@
         <v>118450</v>
       </c>
     </row>
-    <row r="482" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A482" s="1">
         <v>45413</v>
       </c>
@@ -8748,7 +8748,7 @@
         <v>118450</v>
       </c>
     </row>
-    <row r="483" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A483" s="1">
         <v>45444</v>
       </c>
@@ -8765,7 +8765,7 @@
         <v>118300</v>
       </c>
     </row>
-    <row r="484" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A484" s="1">
         <v>45474</v>
       </c>
@@ -8782,7 +8782,7 @@
         <v>118150</v>
       </c>
     </row>
-    <row r="485" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A485" s="1">
         <v>45505</v>
       </c>
@@ -8799,7 +8799,7 @@
         <v>118450</v>
       </c>
     </row>
-    <row r="486" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A486" s="1">
         <v>45536</v>
       </c>
@@ -8816,7 +8816,7 @@
         <v>118450</v>
       </c>
     </row>
-    <row r="487" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A487" s="1">
         <v>45566</v>
       </c>
@@ -8833,7 +8833,7 @@
         <v>121100</v>
       </c>
     </row>
-    <row r="488" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A488" s="1">
         <v>45597</v>
       </c>
@@ -8850,7 +8850,7 @@
         <v>119250</v>
       </c>
     </row>
-    <row r="489" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A489" s="1">
         <v>45627</v>
       </c>
@@ -8867,7 +8867,7 @@
         <v>119400</v>
       </c>
     </row>
-    <row r="490" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A490" s="1">
         <v>45658</v>
       </c>
@@ -8884,7 +8884,7 @@
         <v>119400</v>
       </c>
     </row>
-    <row r="491" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A491" s="1">
         <v>45689</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>116900</v>
       </c>
     </row>
-    <row r="492" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A492" s="1">
         <v>45717</v>
       </c>
@@ -8918,7 +8918,7 @@
         <v>118450</v>
       </c>
     </row>
-    <row r="493" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A493" s="1">
         <v>45748</v>
       </c>
@@ -8935,7 +8935,7 @@
         <v>118750</v>
       </c>
     </row>
-    <row r="494" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A494" s="1">
         <v>45778</v>
       </c>
@@ -8952,7 +8952,7 @@
         <v>117500</v>
       </c>
     </row>
-    <row r="495" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A495" s="1">
         <v>45809</v>
       </c>
@@ -8969,7 +8969,7 @@
         <v>117500</v>
       </c>
     </row>
-    <row r="496" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A496" s="1">
         <v>45839</v>
       </c>
@@ -8986,7 +8986,7 @@
         <v>117500</v>
       </c>
     </row>
-    <row r="497" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A497" s="1">
         <v>45870</v>
       </c>
@@ -9003,7 +9003,7 @@
         <v>118150</v>
       </c>
     </row>
-    <row r="498" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A498" s="1">
         <v>45901</v>
       </c>
@@ -9020,7 +9020,7 @@
         <v>118150</v>
       </c>
     </row>
-    <row r="499" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A499" s="1">
         <v>45931</v>
       </c>
@@ -9037,7 +9037,7 @@
         <v>118750</v>
       </c>
     </row>
-    <row r="500" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A500" s="1">
         <v>45962</v>
       </c>
@@ -9054,7 +9054,7 @@
         <v>120300</v>
       </c>
     </row>
-    <row r="501" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A501" s="1">
         <v>45992</v>
       </c>
@@ -9071,7 +9071,7 @@
         <v>120650</v>
       </c>
     </row>
-    <row r="502" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A502" s="1">
         <v>46023</v>
       </c>
@@ -9088,7 +9088,7 @@
         <v>120300</v>
       </c>
     </row>
-    <row r="503" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A503" s="1">
         <v>46054</v>
       </c>
@@ -9105,7 +9105,7 @@
         <v>121550</v>
       </c>
     </row>
-    <row r="504" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A504" s="1">
         <v>46082</v>
       </c>
@@ -9122,7 +9122,7 @@
         <v>124700</v>
       </c>
     </row>
-    <row r="505" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A505" s="1">
         <v>46113</v>
       </c>
@@ -9139,7 +9139,7 @@
         <v>125950</v>
       </c>
     </row>
-    <row r="506" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A506" s="1">
         <v>45292</v>
       </c>
@@ -9159,7 +9159,7 @@
         <v>118175</v>
       </c>
     </row>
-    <row r="507" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A507" s="1">
         <v>45323</v>
       </c>
@@ -9176,7 +9176,7 @@
         <v>110400</v>
       </c>
     </row>
-    <row r="508" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A508" s="1">
         <v>45352</v>
       </c>
@@ -9193,7 +9193,7 @@
         <v>115400</v>
       </c>
     </row>
-    <row r="509" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A509" s="1">
         <v>45383</v>
       </c>
@@ -9210,7 +9210,7 @@
         <v>117500</v>
       </c>
     </row>
-    <row r="510" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A510" s="1">
         <v>45413</v>
       </c>
@@ -9227,7 +9227,7 @@
         <v>116650</v>
       </c>
     </row>
-    <row r="511" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A511" s="1">
         <v>45444</v>
       </c>
@@ -9244,7 +9244,7 @@
         <v>116650</v>
       </c>
     </row>
-    <row r="512" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A512" s="1">
         <v>45474</v>
       </c>
@@ -9261,7 +9261,7 @@
         <v>115850</v>
       </c>
     </row>
-    <row r="513" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A513" s="1">
         <v>45505</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>115850</v>
       </c>
     </row>
-    <row r="514" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A514" s="1">
         <v>45536</v>
       </c>
@@ -9295,7 +9295,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="515" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A515" s="1">
         <v>45566</v>
       </c>
@@ -9312,7 +9312,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="516" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A516" s="1">
         <v>45597</v>
       </c>
@@ -9329,7 +9329,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="517" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A517" s="1">
         <v>45627</v>
       </c>
@@ -9346,7 +9346,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="518" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A518" s="1">
         <v>45658</v>
       </c>
@@ -9363,7 +9363,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="519" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A519" s="1">
         <v>45689</v>
       </c>
@@ -9380,7 +9380,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="520" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A520" s="1">
         <v>45717</v>
       </c>
@@ -9397,7 +9397,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="521" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A521" s="1">
         <v>45748</v>
       </c>
@@ -9414,7 +9414,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="522" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A522" s="1">
         <v>45778</v>
       </c>
@@ -9431,7 +9431,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="523" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A523" s="1">
         <v>45809</v>
       </c>
@@ -9448,7 +9448,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="524" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A524" s="1">
         <v>45839</v>
       </c>
@@ -9465,7 +9465,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="525" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A525" s="1">
         <v>45870</v>
       </c>
@@ -9482,7 +9482,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="526" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A526" s="1">
         <v>45901</v>
       </c>
@@ -9499,7 +9499,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="527" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A527" s="1">
         <v>45931</v>
       </c>
@@ -9516,7 +9516,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="528" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A528" s="1">
         <v>45962</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>115000</v>
       </c>
     </row>
-    <row r="529" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A529" s="1">
         <v>45992</v>
       </c>
@@ -9550,7 +9550,7 @@
         <v>116650</v>
       </c>
     </row>
-    <row r="530" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A530" s="1">
         <v>46023</v>
       </c>
@@ -9567,7 +9567,7 @@
         <v>116650</v>
       </c>
     </row>
-    <row r="531" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A531" s="1">
         <v>46054</v>
       </c>
@@ -9584,7 +9584,7 @@
         <v>116650</v>
       </c>
     </row>
-    <row r="532" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A532" s="1">
         <v>46082</v>
       </c>
@@ -9601,7 +9601,7 @@
         <v>116650</v>
       </c>
     </row>
-    <row r="533" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A533" s="1">
         <v>46113</v>
       </c>
@@ -9618,7 +9618,7 @@
         <v>116650</v>
       </c>
     </row>
-    <row r="534" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A534" s="1">
         <v>45292</v>
       </c>
@@ -9638,7 +9638,7 @@
         <v>133325</v>
       </c>
     </row>
-    <row r="535" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A535" s="1">
         <v>45323</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="536" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A536" s="1">
         <v>45352</v>
       </c>
@@ -9672,7 +9672,7 @@
         <v>151050</v>
       </c>
     </row>
-    <row r="537" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A537" s="1">
         <v>45383</v>
       </c>
@@ -9689,7 +9689,7 @@
         <v>151050</v>
       </c>
     </row>
-    <row r="538" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A538" s="1">
         <v>45413</v>
       </c>
@@ -9706,7 +9706,7 @@
         <v>150850</v>
       </c>
     </row>
-    <row r="539" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A539" s="1">
         <v>45444</v>
       </c>
@@ -9723,7 +9723,7 @@
         <v>150850</v>
       </c>
     </row>
-    <row r="540" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A540" s="1">
         <v>45474</v>
       </c>
@@ -9740,7 +9740,7 @@
         <v>150850</v>
       </c>
     </row>
-    <row r="541" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A541" s="1">
         <v>45505</v>
       </c>
@@ -9757,7 +9757,7 @@
         <v>150850</v>
       </c>
     </row>
-    <row r="542" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A542" s="1">
         <v>45536</v>
       </c>
@@ -9774,7 +9774,7 @@
         <v>150850</v>
       </c>
     </row>
-    <row r="543" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A543" s="1">
         <v>45566</v>
       </c>
@@ -9791,7 +9791,7 @@
         <v>150400</v>
       </c>
     </row>
-    <row r="544" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A544" s="1">
         <v>45597</v>
       </c>
@@ -9808,7 +9808,7 @@
         <v>150400</v>
       </c>
     </row>
-    <row r="545" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A545" s="1">
         <v>45627</v>
       </c>
@@ -9825,7 +9825,7 @@
         <v>150400</v>
       </c>
     </row>
-    <row r="546" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A546" s="1">
         <v>45658</v>
       </c>
@@ -9842,7 +9842,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="547" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A547" s="1">
         <v>45689</v>
       </c>
@@ -9859,7 +9859,7 @@
         <v>150400</v>
       </c>
     </row>
-    <row r="548" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A548" s="1">
         <v>45717</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>150850</v>
       </c>
     </row>
-    <row r="549" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A549" s="1">
         <v>45748</v>
       </c>
@@ -9893,7 +9893,7 @@
         <v>155500</v>
       </c>
     </row>
-    <row r="550" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A550" s="1">
         <v>45778</v>
       </c>
@@ -9910,7 +9910,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="551" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A551" s="1">
         <v>45809</v>
       </c>
@@ -9927,7 +9927,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="552" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A552" s="1">
         <v>45839</v>
       </c>
@@ -9944,7 +9944,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="553" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A553" s="1">
         <v>45870</v>
       </c>
@@ -9961,7 +9961,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="554" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A554" s="1">
         <v>45901</v>
       </c>
@@ -9978,7 +9978,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="555" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A555" s="1">
         <v>45931</v>
       </c>
@@ -9995,7 +9995,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="556" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A556" s="1">
         <v>45962</v>
       </c>
@@ -10012,7 +10012,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="557" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A557" s="1">
         <v>45992</v>
       </c>
@@ -10029,7 +10029,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="558" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A558" s="1">
         <v>46023</v>
       </c>
@@ -10046,7 +10046,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="559" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A559" s="1">
         <v>46054</v>
       </c>
@@ -10063,7 +10063,7 @@
         <v>149600</v>
       </c>
     </row>
-    <row r="560" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A560" s="1">
         <v>46082</v>
       </c>
@@ -10080,7 +10080,7 @@
         <v>152500</v>
       </c>
     </row>
-    <row r="561" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A561" s="1">
         <v>46113</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>155850</v>
       </c>
     </row>
-    <row r="562" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A562" s="1">
         <v>45292</v>
       </c>
@@ -10114,7 +10114,7 @@
         <v>159400</v>
       </c>
     </row>
-    <row r="563" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A563" s="1">
         <v>45323</v>
       </c>
@@ -10131,7 +10131,7 @@
         <v>158750</v>
       </c>
     </row>
-    <row r="564" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A564" s="1">
         <v>45352</v>
       </c>
@@ -10148,7 +10148,7 @@
         <v>158750</v>
       </c>
     </row>
-    <row r="565" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A565" s="1">
         <v>45383</v>
       </c>
@@ -10165,7 +10165,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="566" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A566" s="1">
         <v>45413</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>163350</v>
       </c>
     </row>
-    <row r="567" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A567" s="1">
         <v>45444</v>
       </c>
@@ -10199,7 +10199,7 @@
         <v>163350</v>
       </c>
     </row>
-    <row r="568" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A568" s="1">
         <v>45474</v>
       </c>
@@ -10216,7 +10216,7 @@
         <v>163950</v>
       </c>
     </row>
-    <row r="569" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A569" s="1">
         <v>45505</v>
       </c>
@@ -10233,7 +10233,7 @@
         <v>168450</v>
       </c>
     </row>
-    <row r="570" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A570" s="1">
         <v>45536</v>
       </c>
@@ -10250,7 +10250,7 @@
         <v>164400</v>
       </c>
     </row>
-    <row r="571" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A571" s="1">
         <v>45566</v>
       </c>
@@ -10267,7 +10267,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="572" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A572" s="1">
         <v>45597</v>
       </c>
@@ -10284,7 +10284,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="573" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A573" s="1">
         <v>45627</v>
       </c>
@@ -10301,7 +10301,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="574" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A574" s="1">
         <v>45658</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="575" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A575" s="1">
         <v>45689</v>
       </c>
@@ -10335,7 +10335,7 @@
         <v>165400</v>
       </c>
     </row>
-    <row r="576" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A576" s="1">
         <v>45717</v>
       </c>
@@ -10352,7 +10352,7 @@
         <v>163750</v>
       </c>
     </row>
-    <row r="577" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A577" s="1">
         <v>45748</v>
       </c>
@@ -10369,7 +10369,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="578" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A578" s="1">
         <v>45778</v>
       </c>
@@ -10386,7 +10386,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="579" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A579" s="1">
         <v>45809</v>
       </c>
@@ -10403,7 +10403,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="580" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A580" s="1">
         <v>45839</v>
       </c>
@@ -10420,7 +10420,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="581" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A581" s="1">
         <v>45870</v>
       </c>
@@ -10437,7 +10437,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="582" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A582" s="1">
         <v>45901</v>
       </c>
@@ -10454,7 +10454,7 @@
         <v>164150</v>
       </c>
     </row>
-    <row r="583" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A583" s="1">
         <v>45931</v>
       </c>
@@ -10471,7 +10471,7 @@
         <v>163350</v>
       </c>
     </row>
-    <row r="584" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A584" s="1">
         <v>45962</v>
       </c>
@@ -10488,7 +10488,7 @@
         <v>163350</v>
       </c>
     </row>
-    <row r="585" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A585" s="1">
         <v>45992</v>
       </c>
@@ -10505,7 +10505,7 @@
         <v>162900</v>
       </c>
     </row>
-    <row r="586" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A586" s="1">
         <v>46023</v>
       </c>
@@ -10522,7 +10522,7 @@
         <v>162900</v>
       </c>
     </row>
-    <row r="587" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A587" s="1">
         <v>46054</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>162900</v>
       </c>
     </row>
-    <row r="588" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A588" s="1">
         <v>46082</v>
       </c>
@@ -10556,7 +10556,7 @@
         <v>162900</v>
       </c>
     </row>
-    <row r="589" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A589" s="1">
         <v>46113</v>
       </c>
@@ -10573,7 +10573,7 @@
         <v>163550</v>
       </c>
     </row>
-    <row r="590" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A590" s="1">
         <v>45292</v>
       </c>
@@ -10590,7 +10590,7 @@
         <v>154100</v>
       </c>
     </row>
-    <row r="591" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A591" s="1">
         <v>45323</v>
       </c>
@@ -10607,7 +10607,7 @@
         <v>154100</v>
       </c>
     </row>
-    <row r="592" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A592" s="1">
         <v>45352</v>
       </c>
@@ -10624,7 +10624,7 @@
         <v>154100</v>
       </c>
     </row>
-    <row r="593" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A593" s="1">
         <v>45383</v>
       </c>
@@ -10641,7 +10641,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="594" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A594" s="1">
         <v>45413</v>
       </c>
@@ -10658,7 +10658,7 @@
         <v>150650</v>
       </c>
     </row>
-    <row r="595" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A595" s="1">
         <v>45444</v>
       </c>
@@ -10675,7 +10675,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="596" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A596" s="1">
         <v>45474</v>
       </c>
@@ -10692,7 +10692,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="597" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A597" s="1">
         <v>45505</v>
       </c>
@@ -10709,7 +10709,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="598" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A598" s="1">
         <v>45536</v>
       </c>
@@ -10726,7 +10726,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="599" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A599" s="1">
         <v>45566</v>
       </c>
@@ -10743,7 +10743,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="600" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A600" s="1">
         <v>45597</v>
       </c>
@@ -10760,7 +10760,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="601" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A601" s="1">
         <v>45627</v>
       </c>
@@ -10777,7 +10777,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="602" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A602" s="1">
         <v>45658</v>
       </c>
@@ -10794,7 +10794,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="603" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A603" s="1">
         <v>45689</v>
       </c>
@@ -10811,7 +10811,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="604" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A604" s="1">
         <v>45717</v>
       </c>
@@ -10828,7 +10828,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="605" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A605" s="1">
         <v>45748</v>
       </c>
@@ -10845,7 +10845,7 @@
         <v>156600</v>
       </c>
     </row>
-    <row r="606" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A606" s="1">
         <v>45778</v>
       </c>
@@ -10862,7 +10862,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="607" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A607" s="1">
         <v>45809</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="608" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A608" s="1">
         <v>45839</v>
       </c>
@@ -10896,7 +10896,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="609" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A609" s="1">
         <v>45870</v>
       </c>
@@ -10913,7 +10913,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="610" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A610" s="1">
         <v>45901</v>
       </c>
@@ -10930,7 +10930,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="611" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A611" s="1">
         <v>45931</v>
       </c>
@@ -10947,7 +10947,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="612" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A612" s="1">
         <v>45962</v>
       </c>
@@ -10964,7 +10964,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="613" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A613" s="1">
         <v>45992</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="614" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A614" s="1">
         <v>46023</v>
       </c>
@@ -10998,7 +10998,7 @@
         <v>157850</v>
       </c>
     </row>
-    <row r="615" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A615" s="1">
         <v>46054</v>
       </c>
@@ -11015,7 +11015,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="616" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A616" s="1">
         <v>46082</v>
       </c>
@@ -11032,7 +11032,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="617" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A617" s="1">
         <v>46113</v>
       </c>
@@ -11049,7 +11049,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="618" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A618" s="1">
         <v>45292</v>
       </c>
@@ -11066,7 +11066,7 @@
         <v>155350</v>
       </c>
     </row>
-    <row r="619" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A619" s="1">
         <v>45323</v>
       </c>
@@ -11083,7 +11083,7 @@
         <v>153550</v>
       </c>
     </row>
-    <row r="620" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A620" s="1">
         <v>45352</v>
       </c>
@@ -11100,7 +11100,7 @@
         <v>146400</v>
       </c>
     </row>
-    <row r="621" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A621" s="1">
         <v>45383</v>
       </c>
@@ -11117,7 +11117,7 @@
         <v>154400</v>
       </c>
     </row>
-    <row r="622" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A622" s="1">
         <v>45413</v>
       </c>
@@ -11134,7 +11134,7 @@
         <v>153550</v>
       </c>
     </row>
-    <row r="623" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A623" s="1">
         <v>45444</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>153550</v>
       </c>
     </row>
-    <row r="624" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A624" s="1">
         <v>45474</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>153750</v>
       </c>
     </row>
-    <row r="625" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A625" s="1">
         <v>45505</v>
       </c>
@@ -11185,7 +11185,7 @@
         <v>153550</v>
       </c>
     </row>
-    <row r="626" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A626" s="1">
         <v>45536</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>152700</v>
       </c>
     </row>
-    <row r="627" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A627" s="1">
         <v>45566</v>
       </c>
@@ -11219,7 +11219,7 @@
         <v>154200</v>
       </c>
     </row>
-    <row r="628" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A628" s="1">
         <v>45597</v>
       </c>
@@ -11236,7 +11236,7 @@
         <v>155200</v>
       </c>
     </row>
-    <row r="629" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A629" s="1">
         <v>45627</v>
       </c>
@@ -11253,7 +11253,7 @@
         <v>155650</v>
       </c>
     </row>
-    <row r="630" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A630" s="1">
         <v>45658</v>
       </c>
@@ -11270,7 +11270,7 @@
         <v>156250</v>
       </c>
     </row>
-    <row r="631" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A631" s="1">
         <v>45689</v>
       </c>
@@ -11287,7 +11287,7 @@
         <v>155000</v>
       </c>
     </row>
-    <row r="632" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A632" s="1">
         <v>45717</v>
       </c>
@@ -11304,7 +11304,7 @@
         <v>156450</v>
       </c>
     </row>
-    <row r="633" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A633" s="1">
         <v>45748</v>
       </c>
@@ -11321,7 +11321,7 @@
         <v>166250</v>
       </c>
     </row>
-    <row r="634" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A634" s="1">
         <v>45778</v>
       </c>
@@ -11338,7 +11338,7 @@
         <v>162300</v>
       </c>
     </row>
-    <row r="635" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A635" s="1">
         <v>45809</v>
       </c>
@@ -11355,7 +11355,7 @@
         <v>161250</v>
       </c>
     </row>
-    <row r="636" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A636" s="1">
         <v>45839</v>
       </c>
@@ -11372,7 +11372,7 @@
         <v>160850</v>
       </c>
     </row>
-    <row r="637" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A637" s="1">
         <v>45870</v>
       </c>
@@ -11389,7 +11389,7 @@
         <v>161250</v>
       </c>
     </row>
-    <row r="638" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A638" s="1">
         <v>45901</v>
       </c>
@@ -11406,7 +11406,7 @@
         <v>161250</v>
       </c>
     </row>
-    <row r="639" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A639" s="1">
         <v>45931</v>
       </c>
@@ -11423,7 +11423,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="640" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A640" s="1">
         <v>45962</v>
       </c>
@@ -11440,7 +11440,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="641" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A641" s="1">
         <v>45992</v>
       </c>
@@ -11457,7 +11457,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="642" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A642" s="1">
         <v>46023</v>
       </c>
@@ -11474,7 +11474,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="643" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A643" s="1">
         <v>46054</v>
       </c>
@@ -11491,7 +11491,7 @@
         <v>159600</v>
       </c>
     </row>
-    <row r="644" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A644" s="1">
         <v>46082</v>
       </c>
@@ -11508,7 +11508,7 @@
         <v>160850</v>
       </c>
     </row>
-    <row r="645" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A645" s="1">
         <v>46113</v>
       </c>
@@ -11525,7 +11525,7 @@
         <v>166250</v>
       </c>
     </row>
-    <row r="646" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A646" s="1">
         <v>45292</v>
       </c>
@@ -11545,7 +11545,7 @@
         <v>148450</v>
       </c>
     </row>
-    <row r="647" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A647" s="1">
         <v>45323</v>
       </c>
@@ -11562,7 +11562,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="648" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A648" s="1">
         <v>45352</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>131900</v>
       </c>
     </row>
-    <row r="649" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A649" s="1">
         <v>45383</v>
       </c>
@@ -11596,7 +11596,7 @@
         <v>131950</v>
       </c>
     </row>
-    <row r="650" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A650" s="1">
         <v>45413</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>131000</v>
       </c>
     </row>
-    <row r="651" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A651" s="1">
         <v>45444</v>
       </c>
@@ -11630,7 +11630,7 @@
         <v>131250</v>
       </c>
     </row>
-    <row r="652" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A652" s="1">
         <v>45474</v>
       </c>
@@ -11647,7 +11647,7 @@
         <v>113750</v>
       </c>
     </row>
-    <row r="653" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A653" s="1">
         <v>45505</v>
       </c>
@@ -11664,7 +11664,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="654" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A654" s="1">
         <v>45536</v>
       </c>
@@ -11681,7 +11681,7 @@
         <v>128150</v>
       </c>
     </row>
-    <row r="655" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A655" s="1">
         <v>45566</v>
       </c>
@@ -11698,7 +11698,7 @@
         <v>130650</v>
       </c>
     </row>
-    <row r="656" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A656" s="1">
         <v>45597</v>
       </c>
@@ -11715,7 +11715,7 @@
         <v>130000</v>
       </c>
     </row>
-    <row r="657" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A657" s="1">
         <v>45627</v>
       </c>
@@ -11732,7 +11732,7 @@
         <v>128150</v>
       </c>
     </row>
-    <row r="658" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A658" s="1">
         <v>45658</v>
       </c>
@@ -11749,7 +11749,7 @@
         <v>118150</v>
       </c>
     </row>
-    <row r="659" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A659" s="1">
         <v>45689</v>
       </c>
@@ -11766,7 +11766,7 @@
         <v>129400</v>
       </c>
     </row>
-    <row r="660" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A660" s="1">
         <v>45717</v>
       </c>
@@ -11783,7 +11783,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="661" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A661" s="1">
         <v>45748</v>
       </c>
@@ -11800,7 +11800,7 @@
         <v>140650</v>
       </c>
     </row>
-    <row r="662" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A662" s="1">
         <v>45778</v>
       </c>
@@ -11817,7 +11817,7 @@
         <v>148150</v>
       </c>
     </row>
-    <row r="663" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A663" s="1">
         <v>45809</v>
       </c>
@@ -11834,7 +11834,7 @@
         <v>148750</v>
       </c>
     </row>
-    <row r="664" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A664" s="1">
         <v>45839</v>
       </c>
@@ -11851,7 +11851,7 @@
         <v>149400</v>
       </c>
     </row>
-    <row r="665" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A665" s="1">
         <v>45870</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>149400</v>
       </c>
     </row>
-    <row r="666" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A666" s="1">
         <v>45901</v>
       </c>
@@ -11885,7 +11885,7 @@
         <v>149400</v>
       </c>
     </row>
-    <row r="667" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A667" s="1">
         <v>45931</v>
       </c>
@@ -11902,7 +11902,7 @@
         <v>148750</v>
       </c>
     </row>
-    <row r="668" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A668" s="1">
         <v>45962</v>
       </c>
@@ -11919,7 +11919,7 @@
         <v>148750</v>
       </c>
     </row>
-    <row r="669" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A669" s="1">
         <v>45992</v>
       </c>
@@ -11936,7 +11936,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="670" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A670" s="1">
         <v>46023</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="671" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="671" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A671" s="1">
         <v>46054</v>
       </c>
@@ -11970,7 +11970,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="672" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="672" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A672" s="1">
         <v>46082</v>
       </c>
@@ -11987,7 +11987,7 @@
         <v>151900</v>
       </c>
     </row>
-    <row r="673" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="673" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A673" s="1">
         <v>46113</v>
       </c>
@@ -12004,7 +12004,7 @@
         <v>160350</v>
       </c>
     </row>
-    <row r="674" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="674" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A674" s="1">
         <v>45292</v>
       </c>
@@ -12021,7 +12021,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="675" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="675" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A675" s="1">
         <v>45323</v>
       </c>
@@ -12038,7 +12038,7 @@
         <v>131900</v>
       </c>
     </row>
-    <row r="676" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="676" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A676" s="1">
         <v>45352</v>
       </c>
@@ -12055,7 +12055,7 @@
         <v>131900</v>
       </c>
     </row>
-    <row r="677" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="677" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A677" s="1">
         <v>45383</v>
       </c>
@@ -12072,7 +12072,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="678" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="678" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A678" s="1">
         <v>45413</v>
       </c>
@@ -12089,7 +12089,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="679" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="679" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A679" s="1">
         <v>45444</v>
       </c>
@@ -12106,7 +12106,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="680" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="680" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A680" s="1">
         <v>45474</v>
       </c>
@@ -12123,7 +12123,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="681" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="681" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A681" s="1">
         <v>45505</v>
       </c>
@@ -12140,7 +12140,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="682" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="682" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A682" s="1">
         <v>45536</v>
       </c>
@@ -12157,7 +12157,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="683" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="683" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A683" s="1">
         <v>45566</v>
       </c>
@@ -12174,7 +12174,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="684" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="684" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A684" s="1">
         <v>45597</v>
       </c>
@@ -12191,7 +12191,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="685" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="685" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A685" s="1">
         <v>45627</v>
       </c>
@@ -12208,7 +12208,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="686" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="686" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A686" s="1">
         <v>45658</v>
       </c>
@@ -12225,7 +12225,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="687" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="687" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A687" s="1">
         <v>45689</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="688" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="688" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A688" s="1">
         <v>45717</v>
       </c>
@@ -12259,7 +12259,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="689" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="689" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A689" s="1">
         <v>45748</v>
       </c>
@@ -12276,7 +12276,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="690" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="690" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A690" s="1">
         <v>45778</v>
       </c>
@@ -12293,7 +12293,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="691" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="691" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A691" s="1">
         <v>45809</v>
       </c>
@@ -12310,7 +12310,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="692" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="692" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A692" s="1">
         <v>45839</v>
       </c>
@@ -12327,7 +12327,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="693" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="693" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A693" s="1">
         <v>45870</v>
       </c>
@@ -12344,7 +12344,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="694" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="694" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A694" s="1">
         <v>45901</v>
       </c>
@@ -12361,7 +12361,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="695" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="695" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A695" s="1">
         <v>45931</v>
       </c>
@@ -12378,7 +12378,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="696" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="696" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A696" s="1">
         <v>45962</v>
       </c>
@@ -12395,7 +12395,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="697" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="697" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A697" s="1">
         <v>45992</v>
       </c>
@@ -12412,7 +12412,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="698" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="698" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A698" s="1">
         <v>46023</v>
       </c>
@@ -12429,7 +12429,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="699" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="699" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A699" s="1">
         <v>46054</v>
       </c>
@@ -12446,7 +12446,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="700" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="700" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A700" s="1">
         <v>46082</v>
       </c>
@@ -12463,7 +12463,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="701" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="701" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A701" s="1">
         <v>46113</v>
       </c>
@@ -12480,7 +12480,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="702" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="702" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A702" s="1">
         <v>45292</v>
       </c>
@@ -12497,7 +12497,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="703" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="703" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A703" s="1">
         <v>45323</v>
       </c>
@@ -12514,7 +12514,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="704" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="704" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A704" s="1">
         <v>45352</v>
       </c>
@@ -12531,7 +12531,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="705" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="705" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A705" s="1">
         <v>45383</v>
       </c>
@@ -12548,7 +12548,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="706" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="706" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A706" s="1">
         <v>45413</v>
       </c>
@@ -12565,7 +12565,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="707" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="707" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A707" s="1">
         <v>45444</v>
       </c>
@@ -12582,7 +12582,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="708" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="708" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A708" s="1">
         <v>45474</v>
       </c>
@@ -12599,7 +12599,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="709" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="709" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A709" s="1">
         <v>45505</v>
       </c>
@@ -12616,7 +12616,7 @@
         <v>123000</v>
       </c>
     </row>
-    <row r="710" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="710" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A710" s="1">
         <v>45536</v>
       </c>
@@ -12633,7 +12633,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="711" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="711" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A711" s="1">
         <v>45566</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="712" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="712" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A712" s="1">
         <v>45597</v>
       </c>
@@ -12667,7 +12667,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="713" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="713" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A713" s="1">
         <v>45627</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="714" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="714" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A714" s="1">
         <v>45658</v>
       </c>
@@ -12701,7 +12701,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="715" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="715" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A715" s="1">
         <v>45689</v>
       </c>
@@ -12718,7 +12718,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="716" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="716" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A716" s="1">
         <v>45717</v>
       </c>
@@ -12735,7 +12735,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="717" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="717" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A717" s="1">
         <v>45748</v>
       </c>
@@ -12752,7 +12752,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="718" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="718" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A718" s="1">
         <v>45778</v>
       </c>
@@ -12769,7 +12769,7 @@
         <v>126000</v>
       </c>
     </row>
-    <row r="719" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="719" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A719" s="1">
         <v>45809</v>
       </c>
@@ -12786,7 +12786,7 @@
         <v>126000</v>
       </c>
     </row>
-    <row r="720" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="720" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A720" s="1">
         <v>45839</v>
       </c>
@@ -12803,7 +12803,7 @@
         <v>126000</v>
       </c>
     </row>
-    <row r="721" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="721" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A721" s="1">
         <v>45870</v>
       </c>
@@ -12820,7 +12820,7 @@
         <v>126000</v>
       </c>
     </row>
-    <row r="722" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="722" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A722" s="1">
         <v>45901</v>
       </c>
@@ -12837,7 +12837,7 @@
         <v>126500</v>
       </c>
     </row>
-    <row r="723" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="723" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A723" s="1">
         <v>45931</v>
       </c>
@@ -12854,7 +12854,7 @@
         <v>126500</v>
       </c>
     </row>
-    <row r="724" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="724" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A724" s="1">
         <v>45962</v>
       </c>
@@ -12871,7 +12871,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="725" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="725" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A725" s="1">
         <v>45992</v>
       </c>
@@ -12888,7 +12888,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="726" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="726" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A726" s="1">
         <v>46023</v>
       </c>
@@ -12905,7 +12905,7 @@
         <v>126900</v>
       </c>
     </row>
-    <row r="727" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="727" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A727" s="1">
         <v>46054</v>
       </c>
@@ -12922,7 +12922,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="728" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="728" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A728" s="1">
         <v>46082</v>
       </c>
@@ -12939,7 +12939,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="729" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="729" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A729" s="1">
         <v>46113</v>
       </c>
@@ -12956,7 +12956,7 @@
         <v>132400</v>
       </c>
     </row>
-    <row r="730" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="730" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A730" s="1">
         <v>45292</v>
       </c>
@@ -12973,7 +12973,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="731" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="731" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A731" s="1">
         <v>45323</v>
       </c>
@@ -12990,7 +12990,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="732" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="732" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A732" s="1">
         <v>45352</v>
       </c>
@@ -13007,7 +13007,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="733" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="733" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A733" s="1">
         <v>45383</v>
       </c>
@@ -13024,7 +13024,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="734" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="734" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A734" s="1">
         <v>45413</v>
       </c>
@@ -13041,7 +13041,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="735" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="735" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A735" s="1">
         <v>45444</v>
       </c>
@@ -13058,7 +13058,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="736" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="736" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A736" s="1">
         <v>45474</v>
       </c>
@@ -13075,7 +13075,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="737" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="737" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A737" s="1">
         <v>45505</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="738" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="738" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A738" s="1">
         <v>45536</v>
       </c>
@@ -13109,7 +13109,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="739" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="739" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A739" s="1">
         <v>45566</v>
       </c>
@@ -13126,7 +13126,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="740" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="740" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A740" s="1">
         <v>45597</v>
       </c>
@@ -13143,7 +13143,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="741" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="741" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A741" s="1">
         <v>45627</v>
       </c>
@@ -13160,7 +13160,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="742" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="742" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A742" s="1">
         <v>45658</v>
       </c>
@@ -13177,7 +13177,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="743" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="743" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A743" s="1">
         <v>45689</v>
       </c>
@@ -13194,7 +13194,7 @@
         <v>138450</v>
       </c>
     </row>
-    <row r="744" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="744" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A744" s="1">
         <v>45717</v>
       </c>
@@ -13211,7 +13211,7 @@
         <v>139400</v>
       </c>
     </row>
-    <row r="745" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="745" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A745" s="1">
         <v>45748</v>
       </c>
@@ -13228,7 +13228,7 @@
         <v>139400</v>
       </c>
     </row>
-    <row r="746" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="746" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A746" s="1">
         <v>45778</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>139400</v>
       </c>
     </row>
-    <row r="747" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="747" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A747" s="1">
         <v>45809</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>139400</v>
       </c>
     </row>
-    <row r="748" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="748" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A748" s="1">
         <v>45839</v>
       </c>
@@ -13279,7 +13279,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="749" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="749" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A749" s="1">
         <v>45870</v>
       </c>
@@ -13296,7 +13296,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="750" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="750" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A750" s="1">
         <v>45901</v>
       </c>
@@ -13313,7 +13313,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="751" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="751" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A751" s="1">
         <v>45931</v>
       </c>
@@ -13330,7 +13330,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="752" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="752" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A752" s="1">
         <v>45962</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="753" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="753" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A753" s="1">
         <v>45992</v>
       </c>
@@ -13364,7 +13364,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="754" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="754" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A754" s="1">
         <v>46023</v>
       </c>
@@ -13381,7 +13381,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="755" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="755" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A755" s="1">
         <v>46054</v>
       </c>
@@ -13398,7 +13398,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="756" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="756" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A756" s="1">
         <v>46082</v>
       </c>
@@ -13415,7 +13415,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="757" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="757" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A757" s="1">
         <v>46113</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>141600</v>
       </c>
     </row>
-    <row r="758" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="758" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A758" s="1">
         <v>45292</v>
       </c>
@@ -13452,7 +13452,7 @@
         <v>142675</v>
       </c>
     </row>
-    <row r="759" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="759" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A759" s="1">
         <v>45323</v>
       </c>
@@ -13469,7 +13469,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="760" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="760" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A760" s="1">
         <v>45352</v>
       </c>
@@ -13486,7 +13486,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="761" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="761" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A761" s="1">
         <v>45383</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="762" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="762" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A762" s="1">
         <v>45413</v>
       </c>
@@ -13520,7 +13520,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="763" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="763" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A763" s="1">
         <v>45444</v>
       </c>
@@ -13537,7 +13537,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="764" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="764" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A764" s="1">
         <v>45474</v>
       </c>
@@ -13554,7 +13554,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="765" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="765" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A765" s="1">
         <v>45505</v>
       </c>
@@ -13571,7 +13571,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="766" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="766" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A766" s="1">
         <v>45536</v>
       </c>
@@ -13588,7 +13588,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="767" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="767" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A767" s="1">
         <v>45566</v>
       </c>
@@ -13605,7 +13605,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="768" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="768" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A768" s="1">
         <v>45597</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="769" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="769" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A769" s="1">
         <v>45627</v>
       </c>
@@ -13639,7 +13639,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="770" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="770" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A770" s="1">
         <v>45658</v>
       </c>
@@ -13656,7 +13656,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="771" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="771" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A771" s="1">
         <v>45689</v>
       </c>
@@ -13673,7 +13673,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="772" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="772" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A772" s="1">
         <v>45717</v>
       </c>
@@ -13690,7 +13690,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="773" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="773" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A773" s="1">
         <v>45748</v>
       </c>
@@ -13707,7 +13707,7 @@
         <v>144400</v>
       </c>
     </row>
-    <row r="774" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="774" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A774" s="1">
         <v>45778</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="775" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="775" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A775" s="1">
         <v>45809</v>
       </c>
@@ -13741,7 +13741,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="776" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="776" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A776" s="1">
         <v>45839</v>
       </c>
@@ -13758,7 +13758,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="777" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="777" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A777" s="1">
         <v>45870</v>
       </c>
@@ -13775,7 +13775,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="778" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="778" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A778" s="1">
         <v>45901</v>
       </c>
@@ -13792,7 +13792,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="779" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="779" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A779" s="1">
         <v>45931</v>
       </c>
@@ -13809,7 +13809,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="780" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="780" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A780" s="1">
         <v>45962</v>
       </c>
@@ -13826,7 +13826,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="781" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="781" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A781" s="1">
         <v>45992</v>
       </c>
@@ -13843,7 +13843,7 @@
         <v>143750</v>
       </c>
     </row>
-    <row r="782" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="782" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A782" s="1">
         <v>46023</v>
       </c>
@@ -13860,7 +13860,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="783" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="783" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A783" s="1">
         <v>46054</v>
       </c>
@@ -13877,7 +13877,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="784" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="784" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A784" s="1">
         <v>46082</v>
       </c>
@@ -13894,7 +13894,7 @@
         <v>146250</v>
       </c>
     </row>
-    <row r="785" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="785" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A785" s="1">
         <v>46113</v>
       </c>
@@ -13911,7 +13911,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="786" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="786" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A786" s="1">
         <v>45292</v>
       </c>
@@ -13928,7 +13928,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="787" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="787" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A787" s="1">
         <v>45323</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="788" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="788" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A788" s="1">
         <v>45352</v>
       </c>
@@ -13962,7 +13962,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="789" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="789" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A789" s="1">
         <v>45383</v>
       </c>
@@ -13979,7 +13979,7 @@
         <v>132500</v>
       </c>
     </row>
-    <row r="790" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="790" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A790" s="1">
         <v>45413</v>
       </c>
@@ -13996,7 +13996,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="791" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="791" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A791" s="1">
         <v>45444</v>
       </c>
@@ -14013,7 +14013,7 @@
         <v>134400</v>
       </c>
     </row>
-    <row r="792" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="792" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A792" s="1">
         <v>45474</v>
       </c>
@@ -14030,7 +14030,7 @@
         <v>133150</v>
       </c>
     </row>
-    <row r="793" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="793" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A793" s="1">
         <v>45505</v>
       </c>
@@ -14047,7 +14047,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="794" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="794" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A794" s="1">
         <v>45536</v>
       </c>
@@ -14064,7 +14064,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="795" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="795" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A795" s="1">
         <v>45566</v>
       </c>
@@ -14081,7 +14081,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="796" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="796" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A796" s="1">
         <v>45597</v>
       </c>
@@ -14098,7 +14098,7 @@
         <v>133150</v>
       </c>
     </row>
-    <row r="797" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="797" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A797" s="1">
         <v>45627</v>
       </c>
@@ -14115,7 +14115,7 @@
         <v>133150</v>
       </c>
     </row>
-    <row r="798" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="798" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A798" s="1">
         <v>45658</v>
       </c>
@@ -14132,7 +14132,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="799" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="799" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A799" s="1">
         <v>45689</v>
       </c>
@@ -14149,7 +14149,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="800" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="800" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A800" s="1">
         <v>45717</v>
       </c>
@@ -14166,7 +14166,7 @@
         <v>134100</v>
       </c>
     </row>
-    <row r="801" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="801" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A801" s="1">
         <v>45748</v>
       </c>
@@ -14183,7 +14183,7 @@
         <v>137850</v>
       </c>
     </row>
-    <row r="802" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="802" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A802" s="1">
         <v>45778</v>
       </c>
@@ -14200,7 +14200,7 @@
         <v>133450</v>
       </c>
     </row>
-    <row r="803" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="803" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A803" s="1">
         <v>45809</v>
       </c>
@@ -14217,7 +14217,7 @@
         <v>132850</v>
       </c>
     </row>
-    <row r="804" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="804" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A804" s="1">
         <v>45839</v>
       </c>
@@ -14234,7 +14234,7 @@
         <v>133150</v>
       </c>
     </row>
-    <row r="805" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="805" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A805" s="1">
         <v>45870</v>
       </c>
@@ -14251,7 +14251,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="806" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="806" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A806" s="1">
         <v>45901</v>
       </c>
@@ -14268,7 +14268,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="807" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="807" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A807" s="1">
         <v>45931</v>
       </c>
@@ -14285,7 +14285,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="808" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="808" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A808" s="1">
         <v>45962</v>
       </c>
@@ -14302,7 +14302,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="809" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="809" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A809" s="1">
         <v>45992</v>
       </c>
@@ -14319,7 +14319,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="810" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="810" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A810" s="1">
         <v>46023</v>
       </c>
@@ -14336,7 +14336,7 @@
         <v>140650</v>
       </c>
     </row>
-    <row r="811" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="811" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A811" s="1">
         <v>46054</v>
       </c>
@@ -14353,7 +14353,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="812" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="812" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A812" s="1">
         <v>46082</v>
       </c>
@@ -14370,7 +14370,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="813" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="813" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A813" s="1">
         <v>46113</v>
       </c>
@@ -14387,7 +14387,7 @@
         <v>156250</v>
       </c>
     </row>
-    <row r="814" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="814" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A814" s="1">
         <v>45292</v>
       </c>
@@ -14404,7 +14404,7 @@
         <v>121650</v>
       </c>
     </row>
-    <row r="815" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="815" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A815" s="1">
         <v>45323</v>
       </c>
@@ -14421,7 +14421,7 @@
         <v>121650</v>
       </c>
     </row>
-    <row r="816" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="816" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A816" s="1">
         <v>45352</v>
       </c>
@@ -14438,7 +14438,7 @@
         <v>123350</v>
       </c>
     </row>
-    <row r="817" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="817" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A817" s="1">
         <v>45383</v>
       </c>
@@ -14455,7 +14455,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="818" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="818" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A818" s="1">
         <v>45413</v>
       </c>
@@ -14472,7 +14472,7 @@
         <v>126650</v>
       </c>
     </row>
-    <row r="819" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="819" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A819" s="1">
         <v>45444</v>
       </c>
@@ -14489,7 +14489,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="820" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="820" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A820" s="1">
         <v>45474</v>
       </c>
@@ -14506,7 +14506,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="821" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="821" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A821" s="1">
         <v>45505</v>
       </c>
@@ -14523,7 +14523,7 @@
         <v>123350</v>
       </c>
     </row>
-    <row r="822" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="822" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A822" s="1">
         <v>45536</v>
       </c>
@@ -14540,7 +14540,7 @@
         <v>126650</v>
       </c>
     </row>
-    <row r="823" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="823" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A823" s="1">
         <v>45566</v>
       </c>
@@ -14557,7 +14557,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="824" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="824" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A824" s="1">
         <v>45597</v>
       </c>
@@ -14574,7 +14574,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="825" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="825" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A825" s="1">
         <v>45627</v>
       </c>
@@ -14591,7 +14591,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="826" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="826" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A826" s="1">
         <v>45658</v>
       </c>
@@ -14608,7 +14608,7 @@
         <v>125000</v>
       </c>
     </row>
-    <row r="827" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="827" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A827" s="1">
         <v>45689</v>
       </c>
@@ -14625,7 +14625,7 @@
         <v>125850</v>
       </c>
     </row>
-    <row r="828" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="828" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A828" s="1">
         <v>45717</v>
       </c>
@@ -14642,7 +14642,7 @@
         <v>125850</v>
       </c>
     </row>
-    <row r="829" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="829" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A829" s="1">
         <v>45748</v>
       </c>
@@ -14659,7 +14659,7 @@
         <v>127500</v>
       </c>
     </row>
-    <row r="830" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="830" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A830" s="1">
         <v>45778</v>
       </c>
@@ -14676,7 +14676,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="831" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="831" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A831" s="1">
         <v>45809</v>
       </c>
@@ -14693,7 +14693,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="832" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="832" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A832" s="1">
         <v>45839</v>
       </c>
@@ -14710,7 +14710,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="833" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="833" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A833" s="1">
         <v>45870</v>
       </c>
@@ -14727,7 +14727,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="834" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="834" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A834" s="1">
         <v>45901</v>
       </c>
@@ -14744,7 +14744,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="835" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="835" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A835" s="1">
         <v>45931</v>
       </c>
@@ -14761,7 +14761,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="836" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="836" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A836" s="1">
         <v>45962</v>
       </c>
@@ -14778,7 +14778,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="837" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="837" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A837" s="1">
         <v>45992</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="838" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="838" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A838" s="1">
         <v>46023</v>
       </c>
@@ -14812,7 +14812,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="839" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="839" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A839" s="1">
         <v>46054</v>
       </c>
@@ -14829,7 +14829,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="840" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="840" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A840" s="1">
         <v>46082</v>
       </c>
@@ -14846,7 +14846,7 @@
         <v>128350</v>
       </c>
     </row>
-    <row r="841" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="841" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A841" s="1">
         <v>46113</v>
       </c>
@@ -14863,7 +14863,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="842" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="842" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A842" s="1">
         <v>45292</v>
       </c>
@@ -14880,7 +14880,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="843" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="843" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A843" s="1">
         <v>45323</v>
       </c>
@@ -14897,7 +14897,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="844" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="844" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A844" s="1">
         <v>45352</v>
       </c>
@@ -14914,7 +14914,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="845" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="845" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A845" s="1">
         <v>45383</v>
       </c>
@@ -14931,7 +14931,7 @@
         <v>133750</v>
       </c>
     </row>
-    <row r="846" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="846" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A846" s="1">
         <v>45413</v>
       </c>
@@ -14948,7 +14948,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="847" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="847" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A847" s="1">
         <v>45444</v>
       </c>
@@ -14965,7 +14965,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="848" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="848" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A848" s="1">
         <v>45474</v>
       </c>
@@ -14982,7 +14982,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="849" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="849" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A849" s="1">
         <v>45505</v>
       </c>
@@ -14999,7 +14999,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="850" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="850" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A850" s="1">
         <v>45536</v>
       </c>
@@ -15016,7 +15016,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="851" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="851" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A851" s="1">
         <v>45566</v>
       </c>
@@ -15033,7 +15033,7 @@
         <v>138150</v>
       </c>
     </row>
-    <row r="852" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="852" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A852" s="1">
         <v>45597</v>
       </c>
@@ -15050,7 +15050,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="853" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="853" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A853" s="1">
         <v>45627</v>
       </c>
@@ -15067,7 +15067,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="854" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="854" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A854" s="1">
         <v>45658</v>
       </c>
@@ -15084,7 +15084,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="855" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="855" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A855" s="1">
         <v>45689</v>
       </c>
@@ -15101,7 +15101,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="856" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="856" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A856" s="1">
         <v>45717</v>
       </c>
@@ -15118,7 +15118,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="857" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="857" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A857" s="1">
         <v>45748</v>
       </c>
@@ -15135,7 +15135,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="858" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="858" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A858" s="1">
         <v>45778</v>
       </c>
@@ -15152,7 +15152,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="859" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="859" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A859" s="1">
         <v>45809</v>
       </c>
@@ -15169,7 +15169,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="860" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A860" s="1">
         <v>45839</v>
       </c>
@@ -15186,7 +15186,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="861" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A861" s="1">
         <v>45870</v>
       </c>
@@ -15203,7 +15203,7 @@
         <v>136250</v>
       </c>
     </row>
-    <row r="862" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A862" s="1">
         <v>45901</v>
       </c>
@@ -15220,7 +15220,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="863" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A863" s="1">
         <v>45931</v>
       </c>
@@ -15237,7 +15237,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="864" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A864" s="1">
         <v>45962</v>
       </c>
@@ -15254,7 +15254,7 @@
         <v>136900</v>
       </c>
     </row>
-    <row r="865" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A865" s="1">
         <v>45992</v>
       </c>
@@ -15271,7 +15271,7 @@
         <v>141250</v>
       </c>
     </row>
-    <row r="866" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A866" s="1">
         <v>46023</v>
       </c>
@@ -15288,7 +15288,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="867" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="867" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A867" s="1">
         <v>46054</v>
       </c>
@@ -15305,7 +15305,7 @@
         <v>153750</v>
       </c>
     </row>
-    <row r="868" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A868" s="1">
         <v>46082</v>
       </c>
@@ -15322,7 +15322,7 @@
         <v>148750</v>
       </c>
     </row>
-    <row r="869" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A869" s="1">
         <v>46113</v>
       </c>
@@ -15339,7 +15339,7 @@
         <v>151250</v>
       </c>
     </row>
-    <row r="870" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="870" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A870" s="1">
         <v>45292</v>
       </c>
@@ -15359,7 +15359,7 @@
         <v>144375</v>
       </c>
     </row>
-    <row r="871" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="871" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A871" s="1">
         <v>45323</v>
       </c>
@@ -15376,7 +15376,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="872" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="872" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A872" s="1">
         <v>45352</v>
       </c>
@@ -15393,7 +15393,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="873" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="873" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A873" s="1">
         <v>45383</v>
       </c>
@@ -15410,7 +15410,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="874" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A874" s="1">
         <v>45413</v>
       </c>
@@ -15427,7 +15427,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="875" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A875" s="1">
         <v>45444</v>
       </c>
@@ -15444,7 +15444,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="876" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="876" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A876" s="1">
         <v>45474</v>
       </c>
@@ -15461,7 +15461,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="877" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="877" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A877" s="1">
         <v>45505</v>
       </c>
@@ -15478,7 +15478,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="878" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="878" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A878" s="1">
         <v>45536</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="879" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="879" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A879" s="1">
         <v>45566</v>
       </c>
@@ -15512,7 +15512,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="880" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="880" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A880" s="1">
         <v>45597</v>
       </c>
@@ -15529,7 +15529,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="881" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="881" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A881" s="1">
         <v>45627</v>
       </c>
@@ -15546,7 +15546,7 @@
         <v>137500</v>
       </c>
     </row>
-    <row r="882" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="882" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A882" s="1">
         <v>45658</v>
       </c>
@@ -15566,7 +15566,7 @@
         <v>138750</v>
       </c>
     </row>
-    <row r="883" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="883" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A883" s="1">
         <v>45689</v>
       </c>
@@ -15583,7 +15583,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="884" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="884" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A884" s="1">
         <v>45717</v>
       </c>
@@ -15600,7 +15600,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="885" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="885" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A885" s="1">
         <v>45748</v>
       </c>
@@ -15617,7 +15617,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="886" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="886" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A886" s="1">
         <v>45778</v>
       </c>
@@ -15634,7 +15634,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="887" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="887" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A887" s="1">
         <v>45809</v>
       </c>
@@ -15651,7 +15651,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="888" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="888" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A888" s="1">
         <v>45839</v>
       </c>
@@ -15668,7 +15668,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="889" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="889" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A889" s="1">
         <v>45870</v>
       </c>
@@ -15685,7 +15685,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="890" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="890" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A890" s="1">
         <v>45901</v>
       </c>
@@ -15702,7 +15702,7 @@
         <v>140000</v>
       </c>
     </row>
-    <row r="891" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="891" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A891" s="1">
         <v>45931</v>
       </c>
@@ -15719,7 +15719,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="892" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="892" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A892" s="1">
         <v>45962</v>
       </c>
@@ -15736,7 +15736,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="893" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="893" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A893" s="1">
         <v>45992</v>
       </c>
@@ -15753,7 +15753,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="894" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="894" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A894" s="1">
         <v>46023</v>
       </c>
@@ -15770,7 +15770,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="895" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="895" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A895" s="1">
         <v>46054</v>
       </c>
@@ -15787,7 +15787,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="896" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="896" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A896" s="1">
         <v>46082</v>
       </c>
@@ -15804,7 +15804,7 @@
         <v>145000</v>
       </c>
     </row>
-    <row r="897" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="897" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A897" s="1">
         <v>46113</v>
       </c>
@@ -15821,7 +15821,7 @@
         <v>150000</v>
       </c>
     </row>
-    <row r="898" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="898" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A898" s="1">
         <v>45292</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>141925</v>
       </c>
     </row>
-    <row r="899" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="899" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A899" s="1">
         <v>45323</v>
       </c>
@@ -15858,7 +15858,7 @@
         <v>133850</v>
       </c>
     </row>
-    <row r="900" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="900" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A900" s="1">
         <v>45352</v>
       </c>
@@ -15875,7 +15875,7 @@
         <v>133650</v>
       </c>
     </row>
-    <row r="901" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="901" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A901" s="1">
         <v>45383</v>
       </c>
@@ -15892,7 +15892,7 @@
         <v>136750</v>
       </c>
     </row>
-    <row r="902" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="902" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A902" s="1">
         <v>45413</v>
       </c>
@@ -15912,7 +15912,7 @@
         <v>135725</v>
       </c>
     </row>
-    <row r="903" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="903" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A903" s="1">
         <v>45444</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="904" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="904" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A904" s="1">
         <v>45474</v>
       </c>
@@ -15946,7 +15946,7 @@
         <v>135550</v>
       </c>
     </row>
-    <row r="905" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="905" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A905" s="1">
         <v>45505</v>
       </c>
@@ -15963,7 +15963,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="906" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="906" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A906" s="1">
         <v>45536</v>
       </c>
@@ -15980,7 +15980,7 @@
         <v>135000</v>
       </c>
     </row>
-    <row r="907" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="907" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A907" s="1">
         <v>45566</v>
       </c>
@@ -15997,7 +15997,7 @@
         <v>134700</v>
       </c>
     </row>
-    <row r="908" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="908" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A908" s="1">
         <v>45597</v>
       </c>
@@ -16014,7 +16014,7 @@
         <v>134800</v>
       </c>
     </row>
-    <row r="909" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="909" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A909" s="1">
         <v>45627</v>
       </c>
@@ -16031,7 +16031,7 @@
         <v>134400</v>
       </c>
     </row>
-    <row r="910" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="910" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A910" s="1">
         <v>45658</v>
       </c>
@@ -16048,7 +16048,7 @@
         <v>136550</v>
       </c>
     </row>
-    <row r="911" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="911" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A911" s="1">
         <v>45689</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>135300</v>
       </c>
     </row>
-    <row r="912" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="912" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A912" s="1">
         <v>45717</v>
       </c>
@@ -16082,7 +16082,7 @@
         <v>135650</v>
       </c>
     </row>
-    <row r="913" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="913" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A913" s="1">
         <v>45748</v>
       </c>
@@ -16099,7 +16099,7 @@
         <v>158050</v>
       </c>
     </row>
-    <row r="914" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="914" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A914" s="1">
         <v>45778</v>
       </c>
@@ -16116,7 +16116,7 @@
         <v>155450</v>
       </c>
     </row>
-    <row r="915" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="915" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A915" s="1">
         <v>45809</v>
       </c>
@@ -16133,7 +16133,7 @@
         <v>151500</v>
       </c>
     </row>
-    <row r="916" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="916" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A916" s="1">
         <v>45839</v>
       </c>
@@ -16150,7 +16150,7 @@
         <v>151650</v>
       </c>
     </row>
-    <row r="917" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="917" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A917" s="1">
         <v>45870</v>
       </c>
@@ -16167,7 +16167,7 @@
         <v>151550</v>
       </c>
     </row>
-    <row r="918" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="918" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A918" s="1">
         <v>45901</v>
       </c>
@@ -16184,7 +16184,7 @@
         <v>151400</v>
       </c>
     </row>
-    <row r="919" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="919" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A919" s="1">
         <v>45931</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>151400</v>
       </c>
     </row>
-    <row r="920" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="920" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A920" s="1">
         <v>45962</v>
       </c>
@@ -16218,7 +16218,7 @@
         <v>151500</v>
       </c>
     </row>
-    <row r="921" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="921" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A921" s="1">
         <v>45992</v>
       </c>
@@ -16235,7 +16235,7 @@
         <v>151750</v>
       </c>
     </row>
-    <row r="922" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="922" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A922" s="1">
         <v>46023</v>
       </c>
@@ -16252,7 +16252,7 @@
         <v>160300</v>
       </c>
     </row>
-    <row r="923" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="923" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A923" s="1">
         <v>46054</v>
       </c>
@@ -16269,7 +16269,7 @@
         <v>157450</v>
       </c>
     </row>
-    <row r="924" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="924" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A924" s="1">
         <v>46082</v>
       </c>
@@ -16286,7 +16286,7 @@
         <v>157300</v>
       </c>
     </row>
-    <row r="925" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="925" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A925" s="1">
         <v>46113</v>
       </c>
@@ -16303,7 +16303,7 @@
         <v>157800</v>
       </c>
     </row>
-    <row r="926" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="926" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A926" s="1">
         <v>45292</v>
       </c>
@@ -16320,7 +16320,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="927" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="927" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A927" s="1">
         <v>45323</v>
       </c>
@@ -16337,7 +16337,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="928" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="928" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A928" s="1">
         <v>45352</v>
       </c>
@@ -16354,7 +16354,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="929" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="929" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A929" s="1">
         <v>45383</v>
       </c>
@@ -16371,7 +16371,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="930" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="930" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A930" s="1">
         <v>45413</v>
       </c>
@@ -16388,7 +16388,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="931" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="931" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A931" s="1">
         <v>45444</v>
       </c>
@@ -16405,7 +16405,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="932" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="932" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A932" s="1">
         <v>45474</v>
       </c>
@@ -16422,7 +16422,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="933" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="933" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A933" s="1">
         <v>45505</v>
       </c>
@@ -16439,7 +16439,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="934" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="934" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A934" s="1">
         <v>45536</v>
       </c>
@@ -16456,7 +16456,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="935" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="935" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A935" s="1">
         <v>45566</v>
       </c>
@@ -16473,7 +16473,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="936" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="936" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A936" s="1">
         <v>45597</v>
       </c>
@@ -16490,7 +16490,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="937" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="937" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A937" s="1">
         <v>45627</v>
       </c>
@@ -16507,7 +16507,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="938" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="938" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A938" s="1">
         <v>45658</v>
       </c>
@@ -16524,7 +16524,7 @@
         <v>152500</v>
       </c>
     </row>
-    <row r="939" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="939" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A939" s="1">
         <v>45689</v>
       </c>
@@ -16541,7 +16541,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="940" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="940" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A940" s="1">
         <v>45717</v>
       </c>
@@ -16558,7 +16558,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="941" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="941" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A941" s="1">
         <v>45748</v>
       </c>
@@ -16575,7 +16575,7 @@
         <v>152500</v>
       </c>
     </row>
-    <row r="942" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="942" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A942" s="1">
         <v>45778</v>
       </c>
@@ -16592,7 +16592,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="943" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="943" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A943" s="1">
         <v>45809</v>
       </c>
@@ -16609,7 +16609,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="944" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="944" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A944" s="1">
         <v>45839</v>
       </c>
@@ -16626,7 +16626,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="945" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="945" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A945" s="1">
         <v>45870</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="946" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="946" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A946" s="1">
         <v>45901</v>
       </c>
@@ -16660,7 +16660,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="947" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="947" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A947" s="1">
         <v>45931</v>
       </c>
@@ -16677,7 +16677,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="948" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="948" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A948" s="1">
         <v>45962</v>
       </c>
@@ -16694,7 +16694,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="949" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="949" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A949" s="1">
         <v>45992</v>
       </c>
@@ -16711,7 +16711,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="950" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="950" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A950" s="1">
         <v>46023</v>
       </c>
@@ -16728,7 +16728,7 @@
         <v>152500</v>
       </c>
     </row>
-    <row r="951" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="951" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A951" s="1">
         <v>46054</v>
       </c>
@@ -16745,7 +16745,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="952" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="952" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A952" s="1">
         <v>46082</v>
       </c>
@@ -16762,7 +16762,7 @@
         <v>147500</v>
       </c>
     </row>
-    <row r="953" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="953" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A953" s="1">
         <v>46113</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>152500</v>
       </c>
     </row>
-    <row r="954" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="954" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D954" s="6"/>
     </row>
   </sheetData>
